--- a/human_resources_forms/007_employee_happiness_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/007_employee_happiness_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Job Status</t>
+          <t>Job Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prophets</t>
+          <t>Prophets 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'human_resources'}</t>
+          <t>human_resources</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Human Resources'}</t>
+          <t>Human Resources</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'junior'}</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Junior'}</t>
+          <t>Junior</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'senior'}</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Senior'}</t>
+          <t>Senior</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'contract'}</t>
+          <t>contract</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Contract'}</t>
+          <t>Contract</t>
         </is>
       </c>
     </row>
